--- a/olympic_simulator/media/simulacion_UEFA Conference League_1880.xlsx
+++ b/olympic_simulator/media/simulacion_UEFA Conference League_1880.xlsx
@@ -489,29 +489,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -520,29 +520,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Majestic FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
         <v>6</v>
       </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -551,29 +551,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -582,7 +582,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Milo FC</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -598,13 +598,13 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>-11</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="9">
@@ -639,52 +639,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Milo FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Majestic FC</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Majestic FC</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -693,84 +693,84 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Milo FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Majestic FC</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Milo FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Milo FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Majestic FC</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -783,73 +783,73 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Majestic FC</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Milo FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Milo FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Majestic FC</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -863,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,29 +926,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -957,29 +957,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Chelsea FC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -988,29 +988,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -1019,29 +1019,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -1050,26 +1050,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>El Gouhna FC</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
         <v>7</v>
@@ -1081,29 +1081,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -1112,29 +1112,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Majestic FC</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" t="n">
         <v>13</v>
       </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>16</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8</v>
-      </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1143,14 +1143,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Internazionale</t>
+          <t>ENPPI SC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -1159,13 +1159,13 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
         <v>6</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1174,29 +1174,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AS Soliman</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
         <v>12</v>
       </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13</v>
-      </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1205,29 +1205,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1236,29 +1236,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Raja CA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
         <v>8</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Majestic FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1280,16 +1280,16 @@
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1298,29 +1298,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
         <v>10</v>
       </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>7</v>
       </c>
-      <c r="H15" t="n">
-        <v>10</v>
-      </c>
       <c r="I15" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1329,29 +1329,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>ES Metlaoui</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1360,29 +1360,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AS Korofina</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
         <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1391,26 +1391,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>El Gouhna FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu FC</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1438,13 +1438,13 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1466,16 +1466,16 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chelsea FC</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1500,10 +1500,10 @@
         <v>3</v>
       </c>
       <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n">
         <v>9</v>
-      </c>
-      <c r="H21" t="n">
-        <v>10</v>
       </c>
       <c r="I21" t="n">
         <v>-1</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Union Touarga</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1534,10 +1534,10 @@
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I22" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23">
@@ -1546,26 +1546,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bechem United FC</t>
+          <t>Bayer 04 Leverkusen</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I23" t="n">
         <v>-2</v>
@@ -1577,17 +1577,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -1596,10 +1596,10 @@
         <v>8</v>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I24" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="25">
@@ -1608,29 +1608,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Sekhukhune United FC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I25" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="26">
@@ -1639,29 +1639,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="27">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1686,13 +1686,13 @@
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I27" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="28">
@@ -1701,29 +1701,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I28" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="29">
@@ -1732,29 +1732,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Rivers United FC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I29" t="n">
-        <v>-14</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="30">
@@ -1763,29 +1763,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I30" t="n">
-        <v>-6</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="31">
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I31" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="32">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Accra Lions FC</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1841,13 +1841,13 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>17</v>
       </c>
       <c r="I32" t="n">
-        <v>-11</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="33">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Milo FC</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1872,39 +1872,70 @@
         <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>13</v>
       </c>
       <c r="I33" t="n">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>Partidos</t>
-        </is>
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Shandong Taishan FC</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>21</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
+          <t>Partidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
           <t>Team 1</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="B38" s="1" t="inlineStr">
         <is>
           <t>Team 2</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>Score 1</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="D38" s="1" t="inlineStr">
         <is>
           <t>Score 2</t>
         </is>
@@ -1984,29 +2015,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -2015,29 +2046,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>El Gouhna FC</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2046,29 +2077,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Union Touarga</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="6">
@@ -2077,29 +2108,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I6" t="n">
-        <v>-14</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="9">
@@ -2134,124 +2165,124 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>El Gouhna FC</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Union Touarga</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Union Touarga</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>El Gouhna FC</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Union Touarga</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>El Gouhna FC</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>El Gouhna FC</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2260,91 +2291,91 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Union Touarga</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Union Touarga</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>El Gouhna FC</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Shandong Taishan FC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>El Gouhna FC</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Union Touarga</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2421,29 +2452,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2452,29 +2483,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2483,29 +2514,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -2514,29 +2545,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="9">
@@ -2571,102 +2602,102 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2679,34 +2710,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2715,52 +2746,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Al Nassr FC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -2769,19 +2800,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2858,29 +2889,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Chelsea FC</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
         <v>12</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2889,29 +2920,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2920,29 +2951,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Rivers United FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="6">
@@ -2951,29 +2982,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chelsea FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="9">
@@ -3008,19 +3039,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Rivers United FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -3031,38 +3062,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Rivers United FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,16 +3102,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Rivers United FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3092,22 +3123,22 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -3116,25 +3147,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Rivers United FC</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3143,28 +3174,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Rivers United FC</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3175,14 +3206,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3193,32 +3224,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Rivers United FC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Al Nassr FC</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3295,29 +3326,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AS Soliman</t>
+          <t>Majestic FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3326,29 +3357,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
         <v>9</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>6</v>
       </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3357,29 +3388,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AS Korofina</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -3388,29 +3419,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="9">
@@ -3445,70 +3476,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AS Korofina</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Majestic FC</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AS Soliman</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AS Korofina</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Majestic FC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AS Soliman</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -3517,30 +3548,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AS Korofina</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AS Soliman</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Majestic FC</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3553,109 +3584,109 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Majestic FC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AS Korofina</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AS Soliman</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AS Korofina</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AS Soliman</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Majestic FC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AS Soliman</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AS Korofina</t>
+          <t>Ayacucho FC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>Majestic FC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Al Ain FC</t>
+          <t>Club Nacional de Football</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3732,29 +3763,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internazionale</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -3763,29 +3794,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Raja CA</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -3794,29 +3825,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bechem United FC</t>
+          <t>Sekhukhune United FC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="6">
@@ -3825,29 +3856,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Accra Lions FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>-6</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="9">
@@ -3882,52 +3913,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Sekhukhune United FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Internazionale</t>
+          <t>Raja CA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bechem United FC</t>
+          <t>Accra Lions FC</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Sekhukhune United FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bechem United FC</t>
+          <t>Accra Lions FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -3936,70 +3967,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Internazionale</t>
+          <t>Raja CA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Sekhukhune United FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bechem United FC</t>
+          <t>Accra Lions FC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Internazionale</t>
+          <t>Raja CA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Internazionale</t>
+          <t>Raja CA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Sekhukhune United FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -4008,88 +4039,88 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bechem United FC</t>
+          <t>Accra Lions FC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bechem United FC</t>
+          <t>Accra Lions FC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Sekhukhune United FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Internazionale</t>
+          <t>Raja CA</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Liga de Quito</t>
+          <t>Sekhukhune United FC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Internazionale</t>
+          <t>Raja CA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bechem United FC</t>
+          <t>Accra Lions FC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -4169,26 +4200,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>ENPPI SC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
@@ -4200,29 +4231,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>ES Metlaoui</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
         <v>10</v>
       </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -4231,29 +4262,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
         <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4262,29 +4293,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="9">
@@ -4319,30 +4350,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>ENPPI SC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>ES Metlaoui</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4355,181 +4386,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>ES Metlaoui</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>ENPPI SC</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>ENPPI SC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>ES Metlaoui</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>ES Metlaoui</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>ENPPI SC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>ES Metlaoui</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>ENPPI SC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>York United FC</t>
+          <t>ENPPI SC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lamphun Warriors FC</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC</t>
+          <t>ES Metlaoui</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4606,29 +4637,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -4637,7 +4668,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>El Gouhna FC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4653,13 +4684,13 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
         <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -4668,29 +4699,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Bayer 04 Leverkusen</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="6">
@@ -4699,7 +4730,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4715,13 +4746,13 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="9">
@@ -4756,217 +4787,217 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Bayer 04 Leverkusen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>El Gouhna FC</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Bayer 04 Leverkusen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>El Gouhna FC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Bayer 04 Leverkusen</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>El Gouhna FC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Bayer 04 Leverkusen</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>El Gouhna FC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>El Gouhna FC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Bayer 04 Leverkusen</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pakhtakor FC</t>
+          <t>Bayer 04 Leverkusen</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua FC</t>
+          <t>El Gouhna FC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4980,7 +5011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5043,29 +5074,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -5074,7 +5105,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea FC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5090,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -5105,17 +5136,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -5124,10 +5155,10 @@
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5136,7 +5167,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5149,16 +5180,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5167,7 +5198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5183,10 +5214,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -5198,7 +5229,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>ENPPI SC</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5214,13 +5245,13 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5248,10 +5279,10 @@
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
@@ -5260,7 +5291,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>El Gouhna FC</t>
+          <t>Raja CA</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5276,13 +5307,13 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="11">
@@ -5291,7 +5322,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daegu FC</t>
+          <t>El Gouhna FC</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5307,10 +5338,10 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>-1</v>
@@ -5322,7 +5353,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Internazionale</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -5338,10 +5369,10 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>-1</v>
@@ -5353,7 +5384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5369,13 +5400,13 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
@@ -5384,7 +5415,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -5403,10 +5434,10 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -5415,7 +5446,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -5434,10 +5465,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
@@ -5446,7 +5477,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AS Soliman</t>
+          <t>ES Metlaoui</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -5465,10 +5496,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17">
@@ -5477,7 +5508,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -5496,81 +5527,94 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Partidos</t>
-        </is>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CA Cerro</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>Partidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>Team 1</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>Team 2</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>Score 1</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>Score 2</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Daegu FC</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Liverpool FC</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CR Flamengo</t>
+          <t>Chelsea FC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Club Atletico Mineiro</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5582,7 +5626,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -5593,29 +5637,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Internazionale</t>
+          <t>Majestic FC</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -5624,30 +5668,30 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Raja CA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Majestic FC</t>
+          <t>Club Universidad de Chile</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AS Soliman</t>
+          <t>CA Cerro</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5660,106 +5704,106 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Umm Salal SC</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>ENPPI SC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>ES Metlaoui</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Chelsea FC</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>FC Barcelona</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>El Gouhna FC</t>
-        </is>
-      </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Majestic FC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Majestic FC</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Raja CA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CA River Plate</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>ENPPI SC</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -5768,54 +5812,72 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Chelsea FC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Atletico de Madrid</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Liverpool FC</t>
+          <t>Internazionale</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SL Benfica</t>
+          <t>Juventus FC</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chelsea FC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Atletico de Madrid</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
         <v>1</v>
       </c>
     </row>
